--- a/JsonConverter/ExcelFiles/InteractableObject.xlsx
+++ b/JsonConverter/ExcelFiles/InteractableObject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\JewelThief\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F63B687-05D7-4C58-B357-4520AEF010CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6636F33-9F50-4631-853A-5C06983BC6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29730" yWindow="2625" windowWidth="22485" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4500" yWindow="1635" windowWidth="22485" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -38,10 +38,6 @@
  추후 아이템 데이터 Id가 담길 예정</t>
   </si>
   <si>
-    <t>가중치 리스트
- 활률(R,E,U,L)</t>
-  </si>
-  <si>
     <t>Mesh 프리팹 경로</t>
   </si>
   <si>
@@ -140,6 +136,12 @@
   </si>
   <si>
     <t>Object_05</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>확률 리스트
+ 활률(R,E,U,L)
+확률의 총 합이 100을 넘으면 안됨</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -355,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -375,6 +377,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -603,7 +608,7 @@
     <col min="7" max="7" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" ht="36" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -619,162 +624,163 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="G2" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>16</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>20</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>21</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" s="13"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="C5" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>25</v>
-      </c>
       <c r="D5" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="17" t="s">
         <v>26</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="C6" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="D6" s="12" t="s">
         <v>30</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>31</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="17"/>
       <c r="G6" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="16"/>
       <c r="F8" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/InteractableObject.xlsx
+++ b/JsonConverter/ExcelFiles/InteractableObject.xlsx
@@ -1,31 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\JewelThief\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6636F33-9F50-4631-853A-5C06983BC6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="4500" yWindow="1635" windowWidth="22485" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="시트1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
   <si>
     <t>데이터 Id</t>
   </si>
   <si>
     <t>오브젝트 이름</t>
+  </si>
+  <si>
+    <t>오브젝트 타입</t>
   </si>
   <si>
     <t>오브젝트 설명</t>
@@ -38,6 +32,14 @@
  추후 아이템 데이터 Id가 담길 예정</t>
   </si>
   <si>
+    <t>확률 리스트
+  활률(R,E,U,L)
+ 확률의 총 합이 100을 넘으면 안됨</t>
+  </si>
+  <si>
+    <t>등장가능 아이템 갯수 최대 치</t>
+  </si>
+  <si>
     <t>Mesh 프리팹 경로</t>
   </si>
   <si>
@@ -53,12 +55,18 @@
     <t>int[]</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
     <t>ObjName</t>
   </si>
   <si>
+    <t>SpawnObjectTypeData</t>
+  </si>
+  <si>
     <t>ObjectComment</t>
   </si>
   <si>
@@ -71,6 +79,9 @@
     <t>RateList</t>
   </si>
   <si>
+    <t>MaxItemCount</t>
+  </si>
+  <si>
     <t>ObjMeshPrefabPath</t>
   </si>
   <si>
@@ -80,6 +91,9 @@
     <t>케비넷</t>
   </si>
   <si>
+    <t>Cabinet</t>
+  </si>
+  <si>
     <t>케비넷이다. 안에는 소모품이 들어있다.</t>
   </si>
   <si>
@@ -95,6 +109,9 @@
     <t>나무상자</t>
   </si>
   <si>
+    <t>WoodBox</t>
+  </si>
+  <si>
     <t>나무상자다. 주로 값 싼 보석이 들어있지만 가끔 좋은 보석이 나오는 경우도 있다.</t>
   </si>
   <si>
@@ -110,6 +127,9 @@
     <t>잠긴금고</t>
   </si>
   <si>
+    <t>LockBox</t>
+  </si>
+  <si>
     <t>금고다. 잠겨있는만큼 값 비싼 보석이 담겨있다. 억지로 금고를 열려는 시도를 하는경우 안에 있는 보석이 상할 수 있다.</t>
   </si>
   <si>
@@ -119,67 +139,49 @@
     <t>Assets/03_Prefabs/Object/Mesh_IronBox_Prefab.prefab</t>
   </si>
   <si>
+    <t>Object_04</t>
+  </si>
+  <si>
     <t>열린금고(도구사용)</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
     <t>0,10,50,40</t>
   </si>
   <si>
+    <t>Object_05</t>
+  </si>
+  <si>
     <t>망가진 금고</t>
   </si>
   <si>
     <t>0,40,50,10</t>
-  </si>
-  <si>
-    <t>Object_04</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_05</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>확률 리스트
- 활률(R,E,U,L)
-확률의 총 합이 100을 넘으면 안됨</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="4">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="&quot;\0022맑은 고딕\0022&quot;"/>
     </font>
   </fonts>
   <fills count="4">
@@ -187,7 +189,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -202,14 +204,8 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="16">
+    <border/>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
@@ -223,10 +219,8 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -236,10 +230,24 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
@@ -249,7 +257,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -258,11 +265,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -277,7 +282,17 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -292,7 +307,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -301,33 +315,30 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+    </border>
+    <border>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <right style="thick">
         <color rgb="FF000000"/>
       </right>
-      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -336,69 +347,110 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+  <cellXfs count="23">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="13" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="14" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="15" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="15" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -588,27 +640,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="3" max="3" width="37.85546875" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="5" width="32.85546875" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" customWidth="1"/>
+    <col customWidth="1" min="3" max="3" width="19.25"/>
+    <col customWidth="1" min="4" max="4" width="37.88"/>
+    <col customWidth="1" min="5" max="5" width="14.25"/>
+    <col customWidth="1" min="6" max="6" width="32.88"/>
+    <col customWidth="1" min="7" max="7" width="17.25"/>
+    <col customWidth="1" min="8" max="9" width="15.38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="36" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -624,163 +674,209 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="18"/>
+      <c r="G4" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="21"/>
+      <c r="G5" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>5</v>
+      <c r="E6" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="21"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22">
+        <v>5.0</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>6</v>
+    <row r="7">
+      <c r="A7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="21"/>
+      <c r="G7" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="22">
+        <v>5.0</v>
+      </c>
+      <c r="I7" s="22" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="13"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="5" t="s">
+    <row r="8">
+      <c r="A8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>31</v>
+      <c r="F8" s="21"/>
+      <c r="G8" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>